--- a/myapp/src/main/resources/plantilla2.xlsx
+++ b/myapp/src/main/resources/plantilla2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\App_TecnoMat\app_lectorArchivos\myapp\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E511188-5588-45F7-AB70-BCE329668F9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6522A4F5-407F-4482-A3C0-0BD06E7943AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5430" yWindow="3345" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4785" yWindow="2820" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Listado" sheetId="1" r:id="rId1"/>
@@ -181,9 +181,6 @@
     <t>MAGNET DX3 6/10 KA C P+N 6A</t>
   </si>
   <si>
-    <t>TS2600010340</t>
-  </si>
-  <si>
     <t>LISTADO ZPATOS</t>
   </si>
   <si>
@@ -194,6 +191,9 @@
   </si>
   <si>
     <t>CHENTE</t>
+  </si>
+  <si>
+    <t>OT2600010340</t>
   </si>
 </sst>
 </file>
@@ -527,6 +527,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -569,7 +570,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -895,12 +895,12 @@
       </c>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
-      <c r="D2" s="36" t="s">
-        <v>54</v>
-      </c>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
+      <c r="D2" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
       <c r="J2" s="8"/>
@@ -928,7 +928,7 @@
         <v>2</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E4" s="16"/>
       <c r="F4" s="7"/>
@@ -946,18 +946,18 @@
         <v>3</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E5" s="20"/>
       <c r="F5" s="7"/>
-      <c r="G5" s="37" t="s">
+      <c r="G5" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="H5" s="37"/>
-      <c r="I5" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="J5" s="39"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="J5" s="40"/>
     </row>
     <row r="6" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
@@ -967,19 +967,19 @@
       <c r="C6" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6" s="41"/>
+      <c r="D6" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="42"/>
       <c r="F6" s="7"/>
-      <c r="G6" s="42" t="s">
+      <c r="G6" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="H6" s="42"/>
-      <c r="I6" s="43">
+      <c r="H6" s="43"/>
+      <c r="I6" s="44">
         <v>46449</v>
       </c>
-      <c r="J6" s="44"/>
+      <c r="J6" s="45"/>
     </row>
     <row r="7" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="6"/>
@@ -988,14 +988,14 @@
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
-      <c r="G7" s="31" t="s">
+      <c r="G7" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="H7" s="31"/>
-      <c r="I7" s="32">
+      <c r="H7" s="32"/>
+      <c r="I7" s="33">
         <v>46111</v>
       </c>
-      <c r="J7" s="33"/>
+      <c r="J7" s="34"/>
     </row>
     <row r="8" spans="1:10" ht="18" x14ac:dyDescent="0.25">
       <c r="A8" s="21" t="s">
@@ -1024,12 +1024,12 @@
       <c r="D9" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="34" t="s">
+      <c r="E9" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="35"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="35"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="36"/>
       <c r="I9" s="27"/>
       <c r="J9" s="26"/>
     </row>
@@ -1802,7 +1802,7 @@
       <c r="J44" s="29"/>
     </row>
     <row r="50" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I50" s="45"/>
+      <c r="I50" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="10">
